--- a/Templates Master/endpoint.xlsx
+++ b/Templates Master/endpoint.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giuse\.gemini\antigravity\scratch\OASIS\Templates Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311B4729-6E5F-416A-9AC5-BBD596C493B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05BB2DD-54DB-4BD9-ADBA-DB881A4C1A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>

--- a/Templates Master/endpoint.xlsx
+++ b/Templates Master/endpoint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giuse\.gemini\antigravity\scratch\OASIS\Templates Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05BB2DD-54DB-4BD9-ADBA-DB881A4C1A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195B8C46-9AF1-421F-9567-056AE8A2360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="23">
   <si>
     <t>Request Parameters</t>
   </si>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t>Request Body</t>
-  </si>
-  <si>
-    <t>Structure of a FPAD account assessment request.</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
   <si>
     <t>Section</t>
@@ -701,12 +695,8 @@
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>17</v>
-      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -722,13 +712,13 @@
     </row>
     <row r="2" spans="1:15" s="4" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -737,7 +727,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
@@ -761,7 +751,7 @@
         <v>12</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>14</v>
@@ -795,10 +785,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +825,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
@@ -854,13 +844,13 @@
     </row>
     <row r="2" spans="1:15" s="4" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -869,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
@@ -893,7 +883,7 @@
         <v>12</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>14</v>
